--- a/data/dividends_info_20260923.xlsx
+++ b/data/dividends_info_20260923.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>45.78499984741211</v>
+        <v>46.11000061035156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1965709299987844</v>
+        <v>0.1951854235712052</v>
       </c>
       <c r="J2" t="n">
         <v>173</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.94999694824219</v>
+        <v>65.84999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.061410208327019</v>
+        <v>1.063022044374228</v>
       </c>
       <c r="J3" t="n">
         <v>152</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.5249999761581421</v>
       </c>
       <c r="I5" t="n">
-        <v>0.784313740156468</v>
+        <v>0.7619047965051923</v>
       </c>
       <c r="J5" t="n">
         <v>82</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45.78499984741211</v>
+        <v>46.11000061035156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1965709299987844</v>
+        <v>0.1951854235712052</v>
       </c>
       <c r="J6" t="n">
         <v>82</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.625</v>
+        <v>24.04000091552734</v>
       </c>
       <c r="I8" t="n">
-        <v>1.142857142857143</v>
+        <v>1.123128077027685</v>
       </c>
       <c r="J8" t="n">
         <v>61</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.36000061035156</v>
+        <v>24.68000030517578</v>
       </c>
       <c r="I9" t="n">
-        <v>2.422003223387789</v>
+        <v>2.390599646290392</v>
       </c>
       <c r="J9" t="n">
         <v>61</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.929999828338623</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I10" t="n">
-        <v>3.372681379251118</v>
+        <v>3.36134464556733</v>
       </c>
       <c r="J10" t="n">
         <v>54</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.77000045776367</v>
+        <v>10.76000022888184</v>
       </c>
       <c r="I11" t="n">
-        <v>4.271123309641125</v>
+        <v>4.27509284586514</v>
       </c>
       <c r="J11" t="n">
         <v>33</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8.050000190734863</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7453415972468785</v>
+        <v>0.7407407058555365</v>
       </c>
       <c r="J12" t="n">
         <v>26</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.5249999761581421</v>
       </c>
       <c r="I13" t="n">
-        <v>0.784313740156468</v>
+        <v>0.7619047965051923</v>
       </c>
       <c r="J13" t="n">
         <v>26</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.059999942779541</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9881423036644182</v>
+        <v>0.980392175195585</v>
       </c>
       <c r="J14" t="n">
         <v>12</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7.320000171661377</v>
+        <v>7.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5191256708860891</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="J15" t="n">
         <v>5</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.625</v>
+        <v>24.04000091552734</v>
       </c>
       <c r="I16" t="n">
-        <v>1.142857142857143</v>
+        <v>1.123128077027685</v>
       </c>
       <c r="J16" t="n">
         <v>-2</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.927000045776367</v>
+        <v>1.942000031471252</v>
       </c>
       <c r="I17" t="n">
-        <v>2.95796567960305</v>
+        <v>2.935118387038182</v>
       </c>
       <c r="J17" t="n">
         <v>-2</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>45.78499984741211</v>
+        <v>46.11000061035156</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1965709299987844</v>
+        <v>0.1951854235712052</v>
       </c>
       <c r="J18" t="n">
         <v>-2</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94.25</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="I19" t="n">
-        <v>1.411140583554377</v>
+        <v>1.412639382309967</v>
       </c>
       <c r="J19" t="n">
         <v>-2</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6.099999904632568</v>
+        <v>6.159999847412109</v>
       </c>
       <c r="I20" t="n">
-        <v>4.918032863773797</v>
+        <v>4.870129990766698</v>
       </c>
       <c r="J20" t="n">
         <v>-9</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.5249999761581421</v>
       </c>
       <c r="I21" t="n">
-        <v>0.784313740156468</v>
+        <v>0.7619047965051923</v>
       </c>
       <c r="J21" t="n">
         <v>-30</v>
@@ -2992,7 +2992,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3002,14 +3002,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3019,14 +3019,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3043,7 +3043,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3060,7 +3060,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3077,7 +3077,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3111,7 +3111,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3128,7 +3128,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3145,7 +3145,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3162,7 +3162,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3179,7 +3179,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3196,7 +3196,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3213,7 +3213,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3230,7 +3230,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3247,7 +3247,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3264,7 +3264,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3281,7 +3281,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3315,7 +3315,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3332,7 +3332,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3383,7 +3383,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3400,7 +3400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3417,7 +3417,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3434,7 +3434,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3451,7 +3451,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3468,7 +3468,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3485,7 +3485,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3512,14 +3512,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3536,7 +3536,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3570,7 +3570,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3587,7 +3587,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3604,7 +3604,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3621,7 +3621,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3648,14 +3648,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3672,7 +3672,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3689,7 +3689,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3740,7 +3740,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3757,7 +3757,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3791,7 +3791,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3808,7 +3808,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3842,7 +3842,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3859,7 +3859,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3876,7 +3876,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3893,7 +3893,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3927,7 +3927,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3944,7 +3944,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3978,7 +3978,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3995,7 +3995,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4005,14 +4005,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4029,7 +4029,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4046,7 +4046,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4080,7 +4080,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4097,7 +4097,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4114,7 +4114,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4131,7 +4131,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4148,7 +4148,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4158,14 +4158,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4199,7 +4199,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4209,14 +4209,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4233,7 +4233,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4250,7 +4250,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4267,7 +4267,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4284,7 +4284,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4318,7 +4318,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4335,7 +4335,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4369,7 +4369,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4386,7 +4386,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4396,14 +4396,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4420,7 +4420,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4488,7 +4488,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4505,7 +4505,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4515,14 +4515,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4556,7 +4556,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4573,7 +4573,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4590,7 +4590,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4607,7 +4607,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4624,7 +4624,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4641,7 +4641,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4658,7 +4658,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4692,7 +4692,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4709,7 +4709,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Dipietro Group S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4777,7 +4777,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4794,7 +4794,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4821,14 +4821,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4862,7 +4862,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4879,7 +4879,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4913,7 +4913,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4940,14 +4940,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4964,7 +4964,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4981,7 +4981,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4991,14 +4991,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5032,7 +5032,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5066,7 +5066,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5083,7 +5083,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5100,7 +5100,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5117,7 +5117,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5134,7 +5134,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5151,7 +5151,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5168,7 +5168,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5236,7 +5236,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5246,14 +5246,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5297,14 +5297,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5450,14 +5450,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5467,14 +5467,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5569,14 +5569,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5586,14 +5586,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5637,14 +5637,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5654,14 +5654,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5671,14 +5671,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5739,14 +5739,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5797,7 +5797,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5807,14 +5807,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5831,7 +5831,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5848,7 +5848,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5858,14 +5858,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5875,14 +5875,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5899,7 +5899,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5909,14 +5909,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -5926,14 +5926,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6005,146 +6005,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Impianti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Indel B S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Telmes S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>